--- a/proposal/09_Risk_Register.xlsx
+++ b/proposal/09_Risk_Register.xlsx
@@ -86,10 +86,10 @@
     <t xml:space="preserve">R02</t>
   </si>
   <si>
-    <t xml:space="preserve">Personal data of investors and contacts stored or contacted without a lawful basis under Saudi or UAE PDPL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consent and lawful-basis fields per contact; outreach flag when consent missing; data protection checkpoint before real data; legal confirms basis per jurisdiction</t>
+    <t xml:space="preserve">Personal data of investors and contacts stored or contacted without a lawful basis under the Malaysian PDPA or the Philippine Data Privacy Act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consent and lawful-basis fields per contact; outreach flag when consent missing; data protection checkpoint before real data; legal confirms basis per jurisdiction; DPO appointed as the amended PDPA requires</t>
   </si>
   <si>
     <t xml:space="preserve">Client legal + PM</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">R03</t>
   </si>
   <si>
-    <t xml:space="preserve">Frontier model availability or terms in GCC regions change during the project (cross-region inference, retention terms)</t>
+    <t xml:space="preserve">Frontier model availability or terms in the Southeast Asian regions change during the project (cross-region inference, retention terms)</t>
   </si>
   <si>
     <t xml:space="preserve">Model gateway abstracts providers; re-verify availability at discovery and before go-live; open-weight fallback evaluated in Phase 3</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">Accuracy</t>
   </si>
   <si>
-    <t xml:space="preserve">Claims extraction precision below target on messy scanned or Arabic documents</t>
+    <t xml:space="preserve">Claims extraction precision below target on messy scanned or non-English documents</t>
   </si>
   <si>
     <t xml:space="preserve">Sample corpus in week 1 includes worst cases; OCR with layout analysis; confidence thresholds route low-confidence extractions to human review; tune prompts and tolerances in pilot</t>
@@ -218,16 +218,16 @@
     <t xml:space="preserve">R11</t>
   </si>
   <si>
-    <t xml:space="preserve">Underestimated effort for Arabic right-to-left interface and bilingual search</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arabic in scope from Phase 1, not retrofitted; UX designer on Arabic layout; per-language evaluation</t>
+    <t xml:space="preserve">Underestimated effort for multilingual search and interface once the true language mix of the corpus is known</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Language mix confirmed in week 1 from the sample corpus; multilingual retrieval in scope from Phase 1, not retrofitted; per-language evaluation and reporting</t>
   </si>
   <si>
     <t xml:space="preserve">Full-stack engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Arabic golden-set scores lag English by more than 10 points</t>
+    <t xml:space="preserve">Any language's golden-set scores lag English by more than 10 points</t>
   </si>
   <si>
     <t xml:space="preserve">R12</t>
@@ -991,7 +991,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
